--- a/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Job Configuration</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,76 +913,142 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KPAFNZ4H6TCNWHHFBVAQNXZ1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KPAFNZ4H6TCNWHHFBVAQNXZ1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Job Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KPAFNZ4HDGK3K7VKTWXCT0P4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KPAFNZ4HDGK3K7VKTWXCT0P4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Job Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KPAFNZ4H0513TQ4A7XGFFFDG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KPAFNZ4H0513TQ4A7XGFFFDG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Employee Configuration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,76 +979,318 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KQ7CJ47XV8ZPDD4M80QX0NQH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ7CJ47XV8ZPDD4M80QX0NQH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Employee Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KQ7CJ47XXD1DE6Q1XDAKTW8F</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ7CJ47XXD1DE6Q1XDAKTW8F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Integration Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KQ6WBBM90YET448K38131N8H</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ6WBBM90YET448K38131N8H</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Import Filter Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KQ6WTF6WERB33T0SWB304JJ5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ6WTF6WERB33T0SWB304JJ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KQ6WBEZ0106KGB8B3EPTSXBV</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ6WBEZ0106KGB8B3EPTSXBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sync Operations</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KQ6WWERHXV8KQ46S1K6ACSZA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ6WWERHXV8KQ46S1K6ACSZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Creation Settings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KQ74V1KSC2RW3ZFH13RT6WEB</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ74V1KSC2RW3ZFH13RT6WEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Updation Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KQ74VK4RN6JNW7S0900KR374</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ74VK4RN6JNW7S0900KR374</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Deactivation Settings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KQ74VSZXMKTXX2EKHSYF4HKT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ74VSZXMKTXX2EKHSYF4HKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Reactivation Settings</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KQ74W9HWKGQW5ET3A5E8TNX5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ74W9HWKGQW5ET3A5E8TNX5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Employee Map</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KQ6XD2XB5BXJD7JW9KK4YEG1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ6XD2XB5BXJD7JW9KK4YEG1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Integration Settings</t>
+          <t>Sync Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sync Operations</t>
+          <t>Sync Operations Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Creation Settings</t>
+          <t>Create Employee Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Updation Settings</t>
+          <t>Update Employee Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deactivation Settings</t>
+          <t>Deactivate Employee Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Reactivation Settings</t>
+          <t>Reactivate Employee Settings</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Employee Map</t>
+          <t>Employee Attribute Map</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KQ6XD2XB5BXJD7JW9KK4YEG1</t>
+          <t>h_01KQEV6X3FFHH6ZQG4XX5SG6ZP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQ6XD2XB5BXJD7JW9KK4YEG1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQEV6X3FFHH6ZQG4XX5SG6ZP</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KQEV6X3FFHH6ZQG4XX5SG6ZP</t>
+          <t>h_01KQEX3Y398N9PP309F5C4MAPM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQEV6X3FFHH6ZQG4XX5SG6ZP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQEX3Y398N9PP309F5C4MAPM</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KQEX3Y394E1BNTEGQR3BE8FX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQEX3Y394E1BNTEGQR3BE8FX</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,7 +1211,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Custom Attribute Configuration</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,76 +1221,142 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KQEX3Y394E1BNTEGQR3BE8FX</t>
+          <t>h_01KSF14YHQ6N8GQ2Q8ZFBVVSYT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQEX3Y394E1BNTEGQR3BE8FX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KSF14YHQ6N8GQ2Q8ZFBVVSYT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Custom Attribute Settings</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KSF14YHQW4BFRN3JDY5T4TR6</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KSF14YHQW4BFRN3JDY5T4TR6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Custom Attribute Map</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KSF14YHQ31HH2JJVFF85G00X</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KSF14YHQ31HH2JJVFF85G00X</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KQEX3Y394E1BNTEGQR3BE8FX</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01KQEX3Y394E1BNTEGQR3BE8FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Integration-Guide/headings.xlsx
@@ -1255,7 +1255,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Custom Attribute Map</t>
+          <t>Attribute Map for Populating Values in Custom Field</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
